--- a/infor-beta/templates/INFOR Deal Workbook Template.xlsx
+++ b/infor-beta/templates/INFOR Deal Workbook Template.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Plugin Workspace/infor-beta-test-main/.claude/worktrees/phase-d-migration-efdba7/infor-beta/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{E4B0A79F-A9D9-4342-85E3-E4B06036B362}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{D246D022-F76B-45EF-9733-0C3E3D7975CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="4" xr2:uid="{15DEB5D9-A807-440B-BAC8-9D13793A6E96}"/>
+    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="4" xr2:uid="{F8433DA5-2B98-4C1B-8613-91441CA5E818}"/>
   </bookViews>
   <sheets>
     <sheet name="captable" sheetId="2" r:id="rId1"/>
@@ -1325,7 +1325,7 @@
     <author>Tate Wilson</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{2E78F0F9-04F4-4F67-849C-07EDE9FD7012}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{62F5729B-747F-4B63-9EDC-5C7A5E96DC06}">
       <text>
         <r>
           <rPr>
@@ -1349,7 +1349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{346234C1-1D43-43B3-9B50-E6B4CF796612}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{396BC527-36E8-4926-836A-37376D2854D6}">
       <text>
         <r>
           <rPr>
@@ -4148,15 +4148,15 @@
   <cellStyles count="11">
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 12" xfId="5" xr:uid="{D1780FD5-8508-4382-AAA7-FD8437872D31}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{9CB265AA-1D72-4B47-A885-3B6F12A8DF02}"/>
-    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{DFA1CE44-D0A8-4CB2-AA30-6F10088E9B3E}"/>
-    <cellStyle name="Normal 2 2 14" xfId="7" xr:uid="{0C798271-2B87-457F-A339-A5A79821AF8A}"/>
-    <cellStyle name="Normal 2 3" xfId="6" xr:uid="{2397E579-2958-4AE4-9955-0CF10098E1D6}"/>
-    <cellStyle name="Normal 5" xfId="1" xr:uid="{A423C9DB-35E6-444F-8714-329A0996E486}"/>
-    <cellStyle name="Note 2" xfId="3" xr:uid="{DB6D81E2-10AD-4A36-8DC2-8FCD0D559507}"/>
-    <cellStyle name="Note 3" xfId="9" xr:uid="{ED942671-F0A9-45F8-871C-5962552F2AF9}"/>
-    <cellStyle name="Percent 2" xfId="8" xr:uid="{7DB0435D-E30C-47E4-BE04-4F79E3BB39C3}"/>
+    <cellStyle name="Normal 12" xfId="5" xr:uid="{86898076-45A6-4B20-9A0C-83FAD676A04B}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{D9CF9D4E-5259-4E95-8C2F-1F9E4E07901B}"/>
+    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{DA38AE19-BEA5-4171-BC79-34E9D65F1D80}"/>
+    <cellStyle name="Normal 2 2 14" xfId="7" xr:uid="{9A90288B-F4A1-47FE-AEA6-1412F73361A7}"/>
+    <cellStyle name="Normal 2 3" xfId="6" xr:uid="{0EC71F29-321D-4B48-8C05-1ECF2FC1FDB7}"/>
+    <cellStyle name="Normal 5" xfId="1" xr:uid="{704E21DB-DBBA-405E-8020-EC67BF59A0E5}"/>
+    <cellStyle name="Note 2" xfId="3" xr:uid="{EE077246-EBF3-42E8-B8F7-F791642E0BBE}"/>
+    <cellStyle name="Note 3" xfId="9" xr:uid="{63A0FF23-E8D2-4002-901C-19C32DB29698}"/>
+    <cellStyle name="Percent 2" xfId="8" xr:uid="{F6C39D71-0B88-49C6-9A56-AC100C507934}"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -4267,7 +4267,7 @@
         <xdr:cNvPr id="2" name="Bloomberg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{84CB8576-4787-4E8D-BEDA-D9EA70192355}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FED7D08-C751-4BC5-9753-B45253CA0826}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4314,7 +4314,7 @@
         <xdr:cNvPr id="3" name="BannerTitle">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6A24C5C5-E10B-4C49-A7A7-99070CC24000}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{756B8D7B-D4E2-4A85-AC6B-CC20195D5D6A}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4662,7 +4662,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FBFF1C6F-19D6-4FAD-B8F6-70F360183BF2}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77CF47F-14D5-48F7-BB6B-4A570E2FCE72}">
   <dimension ref="A1:Q190"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.65"/>
   <cols>
@@ -6740,10 +6740,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10" xr:uid="{19FBADF2-11A5-4F11-A242-ADCF2604DFE5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10" xr:uid="{5F547916-34DA-420B-B2D6-475D746840E9}">
       <formula1>"Treasury Stock, Gross Proceeds"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{F0FE7369-FA9E-49BD-B3EF-85A96BD4272E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{AF131C02-352A-4828-AEFB-76912D43AF2E}">
       <formula1>"ON, OFF"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6754,7 +6754,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{4CD2D4F4-4427-4752-BB33-C7E54048198F}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3368FC2-9983-4453-8DF7-57621F7447C3}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -11717,7 +11717,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{7709BE2A-6457-41F9-937F-421D1F2DB56A}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0406C8-5CF8-40AF-BCA7-95418B298AF7}">
   <dimension ref="A2:CE214"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
@@ -16319,7 +16319,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D4049550-7E89-411D-A36E-5B47A41C066E}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9830DFB-C418-4CCF-BD2D-2ACBB3931E3C}">
   <dimension ref="B1:AC131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -20269,13 +20269,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:J10" xr:uid="{C846398C-B3FF-4DED-94D8-32450FB118C5}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:J10" xr:uid="{5A8BFDA3-5B6D-4913-820D-7D58FC5B06A4}">
       <formula1>"Tree, Summary, Detail"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11:J11" xr:uid="{5922BA21-3714-40E3-BC51-C7B740FB7061}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11:J11" xr:uid="{6FF0B093-0E09-4AF4-83DE-0DBBF60EF218}">
       <formula1>"Ascending,Descending"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:J9" xr:uid="{491F9C67-C269-45E3-B087-4E822791A945}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:J9" xr:uid="{4CD9A056-8A1D-4E13-8B11-8281D3843862}">
       <formula1>"Tree, Summary, Detailed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20285,7 +20285,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E1B92C4A-B42D-48CD-9C5A-67CF4BBC5FC5}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E110AC-5477-4F99-93DA-96A5FB725DB1}">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>

--- a/infor-beta/templates/INFOR Deal Workbook Template.xlsx
+++ b/infor-beta/templates/INFOR Deal Workbook Template.xlsx
@@ -2,15 +2,15 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
-  <workbookPr defaultThemeVersion="202300"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Plugin Workspace/infor-beta-test-main/.claude/worktrees/phase-d-migration-efdba7/infor-beta/templates/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://inforfg1-my.sharepoint.com/personal/twilson_inforfg_com/Documents/Desktop/Plugin Workspace/infor-beta-test-main/.claude/worktrees/nice-wing-1856ed/infor-beta/templates/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{D246D022-F76B-45EF-9733-0C3E3D7975CD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{E1A454A0-3231-4F7C-80B1-EA1BCB927A8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-96" yWindow="-96" windowWidth="20928" windowHeight="12432" activeTab="4" xr2:uid="{F8433DA5-2B98-4C1B-8613-91441CA5E818}"/>
+    <workbookView xWindow="57255" yWindow="-16320" windowWidth="29040" windowHeight="15720" activeTab="4" xr2:uid="{1657CB4B-4EF8-46EF-81D8-8E0FE5C0B24F}"/>
   </bookViews>
   <sheets>
     <sheet name="captable" sheetId="2" r:id="rId1"/>
@@ -1325,7 +1325,7 @@
     <author>Tate Wilson</author>
   </authors>
   <commentList>
-    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{62F5729B-747F-4B63-9EDC-5C7A5E96DC06}">
+    <comment ref="F7" authorId="0" shapeId="0" xr:uid="{B8D69229-426D-4098-B0EC-679A08B04CFF}">
       <text>
         <r>
           <rPr>
@@ -1349,7 +1349,7 @@
         </r>
       </text>
     </comment>
-    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{396BC527-36E8-4926-836A-37376D2854D6}">
+    <comment ref="F16" authorId="0" shapeId="0" xr:uid="{8F231EF9-9D09-4BFC-AE23-29C2F8BCDB9F}">
       <text>
         <r>
           <rPr>
@@ -1976,7 +1976,7 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2042,7 +2042,7 @@
     <font>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2050,7 +2050,7 @@
       <i/>
       <sz val="9"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2282,27 +2282,27 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF000000"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <b/>
       <sz val="11"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2310,14 +2310,14 @@
       <b/>
       <sz val="11"/>
       <color rgb="FFFFFFFF"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
       <color rgb="FF0000FF"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -2333,7 +2333,7 @@
       <u/>
       <sz val="11"/>
       <color theme="10"/>
-      <name val="Aptos Narrow"/>
+      <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
     </font>
@@ -4148,15 +4148,15 @@
   <cellStyles count="11">
     <cellStyle name="Hyperlink" xfId="10" builtinId="8"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 12" xfId="5" xr:uid="{86898076-45A6-4B20-9A0C-83FAD676A04B}"/>
-    <cellStyle name="Normal 2" xfId="2" xr:uid="{D9CF9D4E-5259-4E95-8C2F-1F9E4E07901B}"/>
-    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{DA38AE19-BEA5-4171-BC79-34E9D65F1D80}"/>
-    <cellStyle name="Normal 2 2 14" xfId="7" xr:uid="{9A90288B-F4A1-47FE-AEA6-1412F73361A7}"/>
-    <cellStyle name="Normal 2 3" xfId="6" xr:uid="{0EC71F29-321D-4B48-8C05-1ECF2FC1FDB7}"/>
-    <cellStyle name="Normal 5" xfId="1" xr:uid="{704E21DB-DBBA-405E-8020-EC67BF59A0E5}"/>
-    <cellStyle name="Note 2" xfId="3" xr:uid="{EE077246-EBF3-42E8-B8F7-F791642E0BBE}"/>
-    <cellStyle name="Note 3" xfId="9" xr:uid="{63A0FF23-E8D2-4002-901C-19C32DB29698}"/>
-    <cellStyle name="Percent 2" xfId="8" xr:uid="{F6C39D71-0B88-49C6-9A56-AC100C507934}"/>
+    <cellStyle name="Normal 12" xfId="5" xr:uid="{CE6F2C54-B167-4A06-A185-A08E88556AE8}"/>
+    <cellStyle name="Normal 2" xfId="2" xr:uid="{E07BB963-9BD2-4291-9DCC-E84A5D8D1157}"/>
+    <cellStyle name="Normal 2 2" xfId="4" xr:uid="{79064EB1-16EC-46C8-97BE-49B6E57FFDF5}"/>
+    <cellStyle name="Normal 2 2 14" xfId="7" xr:uid="{CC24B774-A14E-4E93-946B-411DEBB8B627}"/>
+    <cellStyle name="Normal 2 3" xfId="6" xr:uid="{8B71D247-F2C1-45E4-8202-0F42336362B1}"/>
+    <cellStyle name="Normal 5" xfId="1" xr:uid="{492ED451-C913-4D8C-B108-6B7C152506D7}"/>
+    <cellStyle name="Note 2" xfId="3" xr:uid="{2B540818-3094-44A4-BC6B-0E056AC9FB8A}"/>
+    <cellStyle name="Note 3" xfId="9" xr:uid="{52E0B832-6583-47E2-8B6C-50083A6A4F6B}"/>
+    <cellStyle name="Percent 2" xfId="8" xr:uid="{B7FB22F4-8570-4000-BCCD-0596963D611C}"/>
   </cellStyles>
   <dxfs count="12">
     <dxf>
@@ -4258,16 +4258,16 @@
     </xdr:from>
     <xdr:to>
       <xdr:col>4</xdr:col>
-      <xdr:colOff>9525</xdr:colOff>
+      <xdr:colOff>7620</xdr:colOff>
       <xdr:row>3</xdr:row>
-      <xdr:rowOff>180975</xdr:rowOff>
+      <xdr:rowOff>179070</xdr:rowOff>
     </xdr:to>
     <xdr:pic>
       <xdr:nvPicPr>
         <xdr:cNvPr id="2" name="Bloomberg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{1FED7D08-C751-4BC5-9753-B45253CA0826}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{6B2E7406-B3B4-4F31-9146-B15A6CEA09DE}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4314,7 +4314,7 @@
         <xdr:cNvPr id="3" name="BannerTitle">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{756B8D7B-D4E2-4A85-AC6B-CC20195D5D6A}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{04CAF731-D73D-46CA-974B-5ADEB5B5EA6C}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -4347,9 +4347,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="INFORFG">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="INFOR (New)">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -4357,48 +4357,48 @@
         <a:sysClr val="window" lastClr="FFFFFF"/>
       </a:lt1>
       <a:dk2>
-        <a:srgbClr val="0E2841"/>
+        <a:srgbClr val="000000"/>
       </a:dk2>
       <a:lt2>
-        <a:srgbClr val="E8E8E8"/>
+        <a:srgbClr val="FFFFFF"/>
       </a:lt2>
       <a:accent1>
-        <a:srgbClr val="156082"/>
+        <a:srgbClr val="0E213F"/>
       </a:accent1>
       <a:accent2>
-        <a:srgbClr val="E97132"/>
+        <a:srgbClr val="46566E"/>
       </a:accent2>
       <a:accent3>
-        <a:srgbClr val="196B24"/>
+        <a:srgbClr val="ADB9CA"/>
       </a:accent3>
       <a:accent4>
-        <a:srgbClr val="0F9ED5"/>
+        <a:srgbClr val="A4844B"/>
       </a:accent4>
       <a:accent5>
-        <a:srgbClr val="A02B93"/>
+        <a:srgbClr val="767171"/>
       </a:accent5>
       <a:accent6>
-        <a:srgbClr val="4EA72E"/>
+        <a:srgbClr val="E5E3E3"/>
       </a:accent6>
       <a:hlink>
-        <a:srgbClr val="467886"/>
+        <a:srgbClr val="800000"/>
       </a:hlink>
       <a:folHlink>
-        <a:srgbClr val="96607D"/>
+        <a:srgbClr val="333300"/>
       </a:folHlink>
     </a:clrScheme>
     <a:fontScheme name="Office">
       <a:majorFont>
-        <a:latin typeface="Aptos Display" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック Light"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线 Light"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Times New Roman"/>
         <a:font script="Hebr" typeface="Times New Roman"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Angsana New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -4422,35 +4422,18 @@
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:majorFont>
       <a:minorFont>
-        <a:latin typeface="Aptos Narrow" panose="02110004020202020204"/>
+        <a:latin typeface="Calibri" panose="020F0502020204030204"/>
         <a:ea typeface=""/>
         <a:cs typeface=""/>
-        <a:font script="Jpan" typeface="游ゴシック"/>
+        <a:font script="Jpan" typeface="ＭＳ Ｐゴシック"/>
         <a:font script="Hang" typeface="맑은 고딕"/>
-        <a:font script="Hans" typeface="等线"/>
+        <a:font script="Hans" typeface="宋体"/>
         <a:font script="Hant" typeface="新細明體"/>
         <a:font script="Arab" typeface="Arial"/>
         <a:font script="Hebr" typeface="Arial"/>
-        <a:font script="Thai" typeface="Tahoma"/>
+        <a:font script="Thai" typeface="Cordia New"/>
         <a:font script="Ethi" typeface="Nyala"/>
         <a:font script="Beng" typeface="Vrinda"/>
         <a:font script="Gujr" typeface="Shruti"/>
@@ -4474,23 +4457,6 @@
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
         <a:font script="Geor" typeface="Sylfaen"/>
-        <a:font script="Armn" typeface="Arial"/>
-        <a:font script="Bugi" typeface="Leelawadee UI"/>
-        <a:font script="Bopo" typeface="Microsoft JhengHei"/>
-        <a:font script="Java" typeface="Javanese Text"/>
-        <a:font script="Lisu" typeface="Segoe UI"/>
-        <a:font script="Mymr" typeface="Myanmar Text"/>
-        <a:font script="Nkoo" typeface="Ebrima"/>
-        <a:font script="Olck" typeface="Nirmala UI"/>
-        <a:font script="Osma" typeface="Ebrima"/>
-        <a:font script="Phag" typeface="Phagspa"/>
-        <a:font script="Syrn" typeface="Estrangelo Edessa"/>
-        <a:font script="Syrj" typeface="Estrangelo Edessa"/>
-        <a:font script="Syre" typeface="Estrangelo Edessa"/>
-        <a:font script="Sora" typeface="Nirmala UI"/>
-        <a:font script="Tale" typeface="Microsoft Tai Le"/>
-        <a:font script="Talu" typeface="Microsoft New Tai Lue"/>
-        <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
     <a:fmtScheme name="Office">
@@ -4552,6 +4518,13 @@
         </a:gradFill>
       </a:fillStyleLst>
       <a:lnStyleLst>
+        <a:ln w="6350" cap="flat" cmpd="sng" algn="ctr">
+          <a:solidFill>
+            <a:schemeClr val="phClr"/>
+          </a:solidFill>
+          <a:prstDash val="solid"/>
+          <a:miter lim="800000"/>
+        </a:ln>
         <a:ln w="12700" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
@@ -4560,13 +4533,6 @@
           <a:miter lim="800000"/>
         </a:ln>
         <a:ln w="19050" cap="flat" cmpd="sng" algn="ctr">
-          <a:solidFill>
-            <a:schemeClr val="phClr"/>
-          </a:solidFill>
-          <a:prstDash val="solid"/>
-          <a:miter lim="800000"/>
-        </a:ln>
-        <a:ln w="25400" cap="flat" cmpd="sng" algn="ctr">
           <a:solidFill>
             <a:schemeClr val="phClr"/>
           </a:solidFill>
@@ -4631,38 +4597,18 @@
       </a:bgFillStyleLst>
     </a:fmtScheme>
   </a:themeElements>
-  <a:objectDefaults>
-    <a:lnDef>
-      <a:spPr/>
-      <a:bodyPr/>
-      <a:lstStyle/>
-      <a:style>
-        <a:lnRef idx="2">
-          <a:schemeClr val="accent1"/>
-        </a:lnRef>
-        <a:fillRef idx="0">
-          <a:schemeClr val="accent1"/>
-        </a:fillRef>
-        <a:effectRef idx="1">
-          <a:schemeClr val="accent1"/>
-        </a:effectRef>
-        <a:fontRef idx="minor">
-          <a:schemeClr val="tx1"/>
-        </a:fontRef>
-      </a:style>
-    </a:lnDef>
-  </a:objectDefaults>
+  <a:objectDefaults/>
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{2E142A2C-CD16-42D6-873A-C26D2A0506FA}" vid="{1BDDFF52-6CD6-40A5-AB3C-68EB2F1E4D0A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="INFORFG" id="{C40C3476-40F1-4759-AFD9-943D003C1CE8}" vid="{F37651BB-B1AE-4F89-8A90-249B56B9B26D}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A77CF47F-14D5-48F7-BB6B-4A570E2FCE72}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A89C8C0-C42C-4E3F-8560-D2ACA18447FA}">
   <dimension ref="A1:Q190"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="15" customHeight="1" x14ac:dyDescent="0.65"/>
   <cols>
@@ -4746,7 +4692,7 @@
       <c r="E6" s="9"/>
       <c r="F6" s="12">
         <f ca="1">TODAY()-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="H6" s="4"/>
     </row>
@@ -4845,7 +4791,7 @@
     <row r="16" spans="1:10" s="1" customFormat="1" ht="18" customHeight="1" x14ac:dyDescent="0.6">
       <c r="B16" s="31" t="str">
         <f ca="1">CONCATENATE("Share Price (",TEXT(F6,"dd-mmm-yy"),")")</f>
-        <v>Share Price (27-Jul-26)</v>
+        <v>Share Price (28-Jul-26)</v>
       </c>
       <c r="F16" s="33"/>
       <c r="H16" s="4"/>
@@ -6740,10 +6686,10 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="2">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10" xr:uid="{5F547916-34DA-420B-B2D6-475D746840E9}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F10" xr:uid="{B1A5D944-56BA-4A54-98C6-E3FDF6DE9398}">
       <formula1>"Treasury Stock, Gross Proceeds"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{AF131C02-352A-4828-AEFB-76912D43AF2E}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="F11" xr:uid="{788CDE27-AF59-4BF9-8F46-8CCE4BC801FE}">
       <formula1>"ON, OFF"</formula1>
     </dataValidation>
   </dataValidations>
@@ -6754,7 +6700,7 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3368FC2-9983-4453-8DF7-57621F7447C3}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{95C0B9FD-C6DE-42EB-A6EE-46A0DDC0766C}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
@@ -6798,7 +6744,7 @@
       </c>
       <c r="F2" s="136">
         <f ca="1">TODAY()-1</f>
-        <v>46230</v>
+        <v>46231</v>
       </c>
       <c r="K2" s="135"/>
       <c r="L2" s="137" t="s">
@@ -6979,7 +6925,7 @@
       <c r="F7" s="145"/>
       <c r="G7" s="153" t="str">
         <f ca="1">CONCATENATE("(",TEXT($F$2,"dd-mmm-yy"),")")</f>
-        <v>(27-Jul-26)</v>
+        <v>(28-Jul-26)</v>
       </c>
       <c r="H7" s="153" t="str">
         <f>"("&amp;F3&amp;")"</f>
@@ -11717,7 +11663,7 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{0C0406C8-5CF8-40AF-BCA7-95418B298AF7}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A81517B4-BB44-47DD-94CA-54497BE865A3}">
   <dimension ref="A2:CE214"/>
   <sheetFormatPr defaultColWidth="9.33203125" defaultRowHeight="14.4" x14ac:dyDescent="0.4"/>
   <cols>
@@ -16319,7 +16265,7 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A9830DFB-C418-4CCF-BD2D-2ACBB3931E3C}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1EC30963-4B61-44FA-89D1-276735A5317F}">
   <dimension ref="B1:AC131"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.55000000000000004"/>
   <cols>
@@ -20269,13 +20215,13 @@
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="3">
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:J10" xr:uid="{5A8BFDA3-5B6D-4913-820D-7D58FC5B06A4}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I10:J10" xr:uid="{0251CEA7-45ED-4A6B-8E24-0E594E4B2B61}">
       <formula1>"Tree, Summary, Detail"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11:J11" xr:uid="{6FF0B093-0E09-4AF4-83DE-0DBBF60EF218}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I11:J11" xr:uid="{DDFF2616-9E88-404A-A55F-799941F60A0F}">
       <formula1>"Ascending,Descending"</formula1>
     </dataValidation>
-    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:J9" xr:uid="{4CD9A056-8A1D-4E13-8B11-8281D3843862}">
+    <dataValidation type="list" allowBlank="1" showInputMessage="1" showErrorMessage="1" sqref="I9:J9" xr:uid="{333F5203-708D-4A2F-8A3C-9E22D31BC556}">
       <formula1>"Tree, Summary, Detailed"</formula1>
     </dataValidation>
   </dataValidations>
@@ -20285,7 +20231,7 @@
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{24E110AC-5477-4F99-93DA-96A5FB725DB1}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{34144C04-0CE9-49FF-B776-489BB7C4A239}">
   <sheetPr>
     <tabColor theme="7"/>
   </sheetPr>
